--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,1653 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134082508</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660329</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620899</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134082510</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660331</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6620825</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134082516</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>660298</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6620853</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134082688</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660368</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6620840</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134082512</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>660329</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6620830</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134082687</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>660381</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6620789</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134082503</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>660254</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620560</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134082513</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>660304</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6620861</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134082691</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>660398</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6620784</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134082509</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>660316</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6620834</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134082520</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>660325</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6620848</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134082692</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>660335</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6620895</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134082514</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>660370</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6620844</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>111021966</v>
       </c>
       <c r="B2" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>660288.2741932538</v>
+        <v>660289</v>
       </c>
       <c r="R2" t="n">
-        <v>6620979.985618373</v>
+        <v>6620980</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2022-06-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>111021967</v>
       </c>
       <c r="B3" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>660311.5279471036</v>
+        <v>660312</v>
       </c>
       <c r="R3" t="n">
-        <v>6620957.230161493</v>
+        <v>6620957</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,19 +847,9 @@
           <t>2022-06-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,6 +884,1653 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134082687</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>660381</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6620789</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134082688</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>660368</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6620840</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134082691</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>660398</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6620784</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134082692</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58841</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>660335</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6620895</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134082503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>660254</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6620560</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134082508</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>660329</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6620899</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134082509</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>660316</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6620834</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134082510</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>660331</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6620825</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134082512</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>660329</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6620830</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134082513</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>660304</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6620861</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134082514</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>660370</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6620844</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134082516</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>660298</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6620853</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134082520</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58838</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>660325</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6620848</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -890,7 +890,7 @@
         <v>134082687</v>
       </c>
       <c r="B4" t="n">
-        <v>58841</v>
+        <v>58851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>134082688</v>
       </c>
       <c r="B5" t="n">
-        <v>58841</v>
+        <v>58851</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>134082691</v>
       </c>
       <c r="B6" t="n">
-        <v>58841</v>
+        <v>58851</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>134082692</v>
       </c>
       <c r="B7" t="n">
-        <v>58841</v>
+        <v>58851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134082503</v>
+        <v>134139011</v>
       </c>
       <c r="B8" t="n">
-        <v>58838</v>
+        <v>58851</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,51 +1402,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1455,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>660254</v>
+        <v>660305</v>
       </c>
       <c r="R8" t="n">
-        <v>6620560</v>
+        <v>6620855</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1518,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134082508</v>
+        <v>134139015</v>
       </c>
       <c r="B9" t="n">
-        <v>58838</v>
+        <v>58851</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,51 +1509,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1582,10 +1542,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>660329</v>
+        <v>660183</v>
       </c>
       <c r="R9" t="n">
-        <v>6620899</v>
+        <v>6620394</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1612,12 +1572,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1645,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134082509</v>
+        <v>134139016</v>
       </c>
       <c r="B10" t="n">
-        <v>58838</v>
+        <v>58851</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,51 +1616,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1709,10 +1649,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>660316</v>
+        <v>660238</v>
       </c>
       <c r="R10" t="n">
-        <v>6620834</v>
+        <v>6620550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,12 +1679,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134082510</v>
+        <v>134139018</v>
       </c>
       <c r="B11" t="n">
-        <v>58838</v>
+        <v>58851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,51 +1723,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1836,10 +1756,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>660331</v>
+        <v>660434</v>
       </c>
       <c r="R11" t="n">
-        <v>6620825</v>
+        <v>6620619</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1866,12 +1786,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134082512</v>
+        <v>134082503</v>
       </c>
       <c r="B12" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1929,7 +1849,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1944,7 +1864,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1963,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660329</v>
+        <v>660254</v>
       </c>
       <c r="R12" t="n">
-        <v>6620830</v>
+        <v>6620560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1993,12 +1913,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134082513</v>
+        <v>134082508</v>
       </c>
       <c r="B13" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,7 +1976,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2090,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660304</v>
+        <v>660329</v>
       </c>
       <c r="R13" t="n">
-        <v>6620861</v>
+        <v>6620899</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2153,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134082514</v>
+        <v>134082509</v>
       </c>
       <c r="B14" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,7 +2103,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2198,12 +2118,12 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2217,10 +2137,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660370</v>
+        <v>660316</v>
       </c>
       <c r="R14" t="n">
-        <v>6620844</v>
+        <v>6620834</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2280,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134082516</v>
+        <v>134082510</v>
       </c>
       <c r="B15" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2310,7 +2230,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2325,7 +2245,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2344,10 +2264,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>660298</v>
+        <v>660331</v>
       </c>
       <c r="R15" t="n">
-        <v>6620853</v>
+        <v>6620825</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2407,10 +2327,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134082520</v>
+        <v>134082512</v>
       </c>
       <c r="B16" t="n">
-        <v>58838</v>
+        <v>58848</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2437,7 +2357,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2452,12 +2372,12 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2471,10 +2391,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>660325</v>
+        <v>660329</v>
       </c>
       <c r="R16" t="n">
-        <v>6620848</v>
+        <v>6620830</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2531,6 +2451,2635 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134082513</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58848</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>660304</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6620861</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134082514</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58848</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>660370</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6620844</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134082516</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58848</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>660298</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6620853</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134082520</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58848</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>660325</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6620848</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134137563</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>660121</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6620387</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134137564</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>660197</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6620506</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134137565</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>660256</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6620549</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>10 tal grodyngel.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>134137567</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>660181</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6620382</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>134137569</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>660202</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6620341</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>134137576</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>660368</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6620881</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>134137577</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>660553</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6620660</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>134137580</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>660360</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6620839</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Alla romklumpar uttorkade</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134137583</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>660389</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6620799</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134137584</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>660552</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6620661</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>22 romklumpar</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134137585</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>660395</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6620799</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>18 romklumpar</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134137586</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>660390</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6620804</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Minst 30 individer observerade</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134137587</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>660360</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6620836</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134137590</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>660359</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6620838</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>20 romklumpar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134137591</v>
+      </c>
+      <c r="B35" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>660356</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6620844</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst ett 30-tal individer spelandes</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134139010</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>660305</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6620855</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134139014</v>
+      </c>
+      <c r="B37" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>660183</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6620394</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134139017</v>
+      </c>
+      <c r="B38" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>660238</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6620550</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Johannes Måsviken, Ellen Linder</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Johannes Måsviken, Ellen Linder</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Johannes Måsviken, Ellen Linder</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Johannes Måsviken, Ellen Linder</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johannes Måsviken, Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johannes Måsviken, Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johannes Måsviken, Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johannes Måsviken, Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111021966</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111021967</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082687</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082688</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082692</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1495,6 +1530,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139011</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1602,6 +1642,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1709,6 +1754,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139016</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1816,6 +1866,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139018</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082503</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2070,6 +2130,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082508</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2197,6 +2262,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082509</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2324,6 +2394,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082510</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2451,6 +2526,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082512</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2578,6 +2658,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082513</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2705,6 +2790,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082514</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2832,6 +2922,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082516</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2959,6 +3054,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134082520</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3078,6 +3178,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137563</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3197,6 +3302,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137564</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3325,6 +3435,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137565</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3444,6 +3559,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137567</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3559,6 +3679,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137569</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3673,6 +3798,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137576</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3787,6 +3917,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137577</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3906,6 +4041,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137580</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4020,6 +4160,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137583</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4143,6 +4288,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137584</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4266,6 +4416,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137585</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4394,6 +4549,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137586</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4508,6 +4668,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137587</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4631,6 +4796,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137590</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4759,6 +4929,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134137591</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4866,6 +5041,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139010</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4973,6 +5153,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139014</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5080,8 +5265,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1874,10 +1874,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134082503</v>
+        <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58848</v>
+        <v>58856</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,63 +1885,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>660254</v>
+        <v>660791</v>
       </c>
       <c r="R12" t="n">
-        <v>6620560</v>
+        <v>6619964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1968,12 +1944,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1982,31 +1963,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anna Koffman, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082503</t>
+          <t>https://artportalen.se/Sighting/135864904</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134082508</v>
+        <v>134082503</v>
       </c>
       <c r="B13" t="n">
         <v>58848</v>
@@ -2036,7 +2020,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2070,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>660329</v>
+        <v>660254</v>
       </c>
       <c r="R13" t="n">
-        <v>6620899</v>
+        <v>6620560</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2100,12 +2084,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,13 +2116,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082508</t>
+          <t>https://artportalen.se/Sighting/134082503</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134082509</v>
+        <v>134082508</v>
       </c>
       <c r="B14" t="n">
         <v>58848</v>
@@ -2168,7 +2152,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2202,10 +2186,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>660316</v>
+        <v>660329</v>
       </c>
       <c r="R14" t="n">
-        <v>6620834</v>
+        <v>6620899</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2264,13 +2248,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082509</t>
+          <t>https://artportalen.se/Sighting/134082508</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134082510</v>
+        <v>134082509</v>
       </c>
       <c r="B15" t="n">
         <v>58848</v>
@@ -2300,7 +2284,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2315,7 +2299,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2334,10 +2318,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>660331</v>
+        <v>660316</v>
       </c>
       <c r="R15" t="n">
-        <v>6620825</v>
+        <v>6620834</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2396,13 +2380,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082510</t>
+          <t>https://artportalen.se/Sighting/134082509</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134082512</v>
+        <v>134082510</v>
       </c>
       <c r="B16" t="n">
         <v>58848</v>
@@ -2432,7 +2416,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2466,10 +2450,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>660329</v>
+        <v>660331</v>
       </c>
       <c r="R16" t="n">
-        <v>6620830</v>
+        <v>6620825</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2528,13 +2512,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082512</t>
+          <t>https://artportalen.se/Sighting/134082510</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134082513</v>
+        <v>134082512</v>
       </c>
       <c r="B17" t="n">
         <v>58848</v>
@@ -2564,7 +2548,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2579,7 +2563,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2598,10 +2582,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>660304</v>
+        <v>660329</v>
       </c>
       <c r="R17" t="n">
-        <v>6620861</v>
+        <v>6620830</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2660,13 +2644,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082513</t>
+          <t>https://artportalen.se/Sighting/134082512</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134082514</v>
+        <v>134082513</v>
       </c>
       <c r="B18" t="n">
         <v>58848</v>
@@ -2696,7 +2680,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2711,12 +2695,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2730,10 +2714,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>660370</v>
+        <v>660304</v>
       </c>
       <c r="R18" t="n">
-        <v>6620844</v>
+        <v>6620861</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2792,13 +2776,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082514</t>
+          <t>https://artportalen.se/Sighting/134082513</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134082516</v>
+        <v>134082514</v>
       </c>
       <c r="B19" t="n">
         <v>58848</v>
@@ -2828,7 +2812,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2843,12 +2827,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>i par</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>i vatten/simmande</t>
+          <t>i lekdräkt</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2862,10 +2846,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>660298</v>
+        <v>660370</v>
       </c>
       <c r="R19" t="n">
-        <v>6620853</v>
+        <v>6620844</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2924,13 +2908,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082516</t>
+          <t>https://artportalen.se/Sighting/134082514</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134082520</v>
+        <v>134082516</v>
       </c>
       <c r="B20" t="n">
         <v>58848</v>
@@ -2975,12 +2959,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>hane</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>i lekdräkt</t>
+          <t>i vatten/simmande</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2994,10 +2978,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>660325</v>
+        <v>660298</v>
       </c>
       <c r="R20" t="n">
-        <v>6620848</v>
+        <v>6620853</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3056,16 +3040,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134082520</t>
+          <t>https://artportalen.se/Sighting/134082516</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134137563</v>
+        <v>134082520</v>
       </c>
       <c r="B21" t="n">
-        <v>58837</v>
+        <v>58848</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3073,21 +3057,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3102,11 +3086,19 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>ägg</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3118,10 +3110,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>660121</v>
+        <v>660325</v>
       </c>
       <c r="R21" t="n">
-        <v>6620387</v>
+        <v>6620848</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3148,12 +3140,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3174,22 +3166,22 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Ellen Linder, Johannes Måsviken</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137563</t>
+          <t>https://artportalen.se/Sighting/134082520</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134137564</v>
+        <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58837</v>
+        <v>58853</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3197,55 +3189,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>208250</v>
+        <v>208242</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>eDNA</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Odensala, Upl</t>
+          <t>Odensala-Harg, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>660197</v>
+        <v>660791</v>
       </c>
       <c r="R22" t="n">
-        <v>6620506</v>
+        <v>6619964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3272,12 +3248,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,31 +3267,34 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
+          <t>Marlijn Sterenborg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ellen Linder</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Anna Koffman, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137564</t>
+          <t>https://artportalen.se/Sighting/135864905</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134137565</v>
+        <v>134137563</v>
       </c>
       <c r="B23" t="n">
         <v>58837</v>
@@ -3340,7 +3324,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3350,15 +3334,11 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3370,10 +3350,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>660256</v>
+        <v>660121</v>
       </c>
       <c r="R23" t="n">
-        <v>6620549</v>
+        <v>6620387</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3408,11 +3388,6 @@
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>10 tal grodyngel.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3437,13 +3412,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137565</t>
+          <t>https://artportalen.se/Sighting/134137563</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134137567</v>
+        <v>134137564</v>
       </c>
       <c r="B24" t="n">
         <v>58837</v>
@@ -3483,7 +3458,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -3499,10 +3474,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>660181</v>
+        <v>660197</v>
       </c>
       <c r="R24" t="n">
-        <v>6620382</v>
+        <v>6620506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,19 +3530,19 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137567</t>
+          <t>https://artportalen.se/Sighting/134137564</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134137569</v>
+        <v>134137565</v>
       </c>
       <c r="B25" t="n">
         <v>58837</v>
@@ -3597,7 +3572,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3605,9 +3580,17 @@
           <t>ex.</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3619,10 +3602,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>660202</v>
+        <v>660256</v>
       </c>
       <c r="R25" t="n">
-        <v>6620341</v>
+        <v>6620549</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3657,6 +3640,11 @@
           <t>2026-05-11</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>10 tal grodyngel.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3675,19 +3663,19 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ellen Linder, Johannes Måsviken</t>
+          <t>Ellen Linder</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137569</t>
+          <t>https://artportalen.se/Sighting/134137565</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134137576</v>
+        <v>134137567</v>
       </c>
       <c r="B26" t="n">
         <v>58837</v>
@@ -3715,7 +3703,11 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -3723,10 +3715,11 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3738,10 +3731,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>660368</v>
+        <v>660181</v>
       </c>
       <c r="R26" t="n">
-        <v>6620881</v>
+        <v>6620382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3768,12 +3761,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3800,13 +3793,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137576</t>
+          <t>https://artportalen.se/Sighting/134137567</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134137577</v>
+        <v>134137569</v>
       </c>
       <c r="B27" t="n">
         <v>58837</v>
@@ -3834,18 +3827,19 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
           <t>ex.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>ägg</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3857,10 +3851,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>660553</v>
+        <v>660202</v>
       </c>
       <c r="R27" t="n">
-        <v>6620660</v>
+        <v>6620341</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3887,12 +3881,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3919,13 +3913,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137577</t>
+          <t>https://artportalen.se/Sighting/134137569</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134137580</v>
+        <v>134137576</v>
       </c>
       <c r="B28" t="n">
         <v>58837</v>
@@ -3961,7 +3955,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3976,10 +3970,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>660360</v>
+        <v>660368</v>
       </c>
       <c r="R28" t="n">
-        <v>6620839</v>
+        <v>6620881</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4014,11 +4008,6 @@
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Alla romklumpar uttorkade</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4043,13 +4032,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137580</t>
+          <t>https://artportalen.se/Sighting/134137576</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134137583</v>
+        <v>134137577</v>
       </c>
       <c r="B29" t="n">
         <v>58837</v>
@@ -4100,10 +4089,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>660389</v>
+        <v>660553</v>
       </c>
       <c r="R29" t="n">
-        <v>6620799</v>
+        <v>6620660</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4162,13 +4151,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137583</t>
+          <t>https://artportalen.se/Sighting/134137577</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134137584</v>
+        <v>134137580</v>
       </c>
       <c r="B30" t="n">
         <v>58837</v>
@@ -4196,11 +4185,7 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4223,10 +4208,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>660552</v>
+        <v>660360</v>
       </c>
       <c r="R30" t="n">
-        <v>6620661</v>
+        <v>6620839</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4253,17 +4238,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>22 romklumpar</t>
+          <t>Alla romklumpar uttorkade</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4290,13 +4275,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137584</t>
+          <t>https://artportalen.se/Sighting/134137580</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134137585</v>
+        <v>134137583</v>
       </c>
       <c r="B31" t="n">
         <v>58837</v>
@@ -4324,11 +4309,7 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4351,7 +4332,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>660395</v>
+        <v>660389</v>
       </c>
       <c r="R31" t="n">
         <v>6620799</v>
@@ -4381,17 +4362,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>18 romklumpar</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4418,13 +4394,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137585</t>
+          <t>https://artportalen.se/Sighting/134137583</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134137586</v>
+        <v>134137584</v>
       </c>
       <c r="B32" t="n">
         <v>58837</v>
@@ -4454,7 +4430,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4464,15 +4440,10 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4484,10 +4455,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>660390</v>
+        <v>660552</v>
       </c>
       <c r="R32" t="n">
-        <v>6620804</v>
+        <v>6620661</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4524,7 +4495,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 30 individer observerade</t>
+          <t>22 romklumpar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4551,13 +4522,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137586</t>
+          <t>https://artportalen.se/Sighting/134137584</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134137587</v>
+        <v>134137585</v>
       </c>
       <c r="B33" t="n">
         <v>58837</v>
@@ -4585,7 +4556,11 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4608,10 +4583,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>660360</v>
+        <v>660395</v>
       </c>
       <c r="R33" t="n">
-        <v>6620836</v>
+        <v>6620799</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4646,6 +4621,11 @@
           <t>2026-04-10</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>18 romklumpar</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4670,13 +4650,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137587</t>
+          <t>https://artportalen.se/Sighting/134137585</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134137590</v>
+        <v>134137586</v>
       </c>
       <c r="B34" t="n">
         <v>58837</v>
@@ -4706,7 +4686,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4716,10 +4696,15 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ägg</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4731,10 +4716,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>660359</v>
+        <v>660390</v>
       </c>
       <c r="R34" t="n">
-        <v>6620838</v>
+        <v>6620804</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4771,7 +4756,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>20 romklumpar</t>
+          <t>Minst 30 individer observerade</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4798,13 +4783,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137590</t>
+          <t>https://artportalen.se/Sighting/134137586</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134137591</v>
+        <v>134137587</v>
       </c>
       <c r="B35" t="n">
         <v>58837</v>
@@ -4832,11 +4817,7 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>ex.</t>
@@ -4844,15 +4825,10 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>ägg</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4864,10 +4840,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>660356</v>
+        <v>660360</v>
       </c>
       <c r="R35" t="n">
-        <v>6620844</v>
+        <v>6620836</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4902,11 +4878,6 @@
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Minst ett 30-tal individer spelandes</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4931,13 +4902,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134137591</t>
+          <t>https://artportalen.se/Sighting/134137587</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134139010</v>
+        <v>134137590</v>
       </c>
       <c r="B36" t="n">
         <v>58837</v>
@@ -4965,14 +4936,25 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ägg</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4981,10 +4963,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>660305</v>
+        <v>660359</v>
       </c>
       <c r="R36" t="n">
-        <v>6620855</v>
+        <v>6620838</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5011,12 +4993,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>20 romklumpar</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5043,13 +5030,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134139010</t>
+          <t>https://artportalen.se/Sighting/134137590</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134139014</v>
+        <v>134137591</v>
       </c>
       <c r="B37" t="n">
         <v>58837</v>
@@ -5077,14 +5064,30 @@
           <t>Nilsson, 1842</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>eDNA</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -5093,10 +5096,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>660183</v>
+        <v>660356</v>
       </c>
       <c r="R37" t="n">
-        <v>6620394</v>
+        <v>6620844</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5123,12 +5126,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst ett 30-tal individer spelandes</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5155,13 +5163,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134139014</t>
+          <t>https://artportalen.se/Sighting/134137591</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134139017</v>
+        <v>134139010</v>
       </c>
       <c r="B38" t="n">
         <v>58837</v>
@@ -5205,10 +5213,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>660238</v>
+        <v>660305</v>
       </c>
       <c r="R38" t="n">
-        <v>6620550</v>
+        <v>6620855</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5267,7 +5275,467 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134139010</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134139014</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>660183</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6620394</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134139014</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134139017</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58837</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Odensala, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>660238</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6620550</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ellen Linder</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ellen Linder, Johannes Måsviken</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134139017</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135864906</v>
+      </c>
+      <c r="B41" t="n">
+        <v>58842</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Odensala-Harg, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>660791</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6619964</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>eDNA åkergroda, mindre vattensalamander, större vattensalamander. Sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna Koffman, Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864906</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135864917</v>
+      </c>
+      <c r="B42" t="n">
+        <v>58842</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Odensala-Harg, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>660652</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6619909</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Odensala</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Subadult, I vatten/simmandefylld körskada</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>C260136 Groddjursinventering Odensala-Harg 2026</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864917</t>
         </is>
       </c>
     </row>
@@ -5310,6 +5778,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58856</v>
+        <v>58858</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58853</v>
+        <v>58855</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58842</v>
+        <v>58844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58842</v>
+        <v>58844</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58858</v>
+        <v>58859</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58855</v>
+        <v>58856</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58844</v>
+        <v>58845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58844</v>
+        <v>58845</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58859</v>
+        <v>58863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58856</v>
+        <v>58860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58845</v>
+        <v>58849</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58845</v>
+        <v>58849</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58863</v>
+        <v>58864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58860</v>
+        <v>58861</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58849</v>
+        <v>58850</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58849</v>
+        <v>58850</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58864</v>
+        <v>58869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
+          <t>Petter Andersson, Anna Koffman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58861</v>
+        <v>58866</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
+          <t>Petter Andersson, Anna Koffman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58850</v>
+        <v>58855</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna Koffman, Petter Andersson</t>
+          <t>Petter Andersson, Anna Koffman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58850</v>
+        <v>58855</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Petter Andersson, Anna Koffman</t>
+          <t>Anna Koffman, Petter Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Petter Andersson, Anna Koffman</t>
+          <t>Anna Koffman, Petter Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Petter Andersson, Anna Koffman</t>
+          <t>Anna Koffman, Petter Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">

--- a/artfynd/A 51189-2022 artfynd.xlsx
+++ b/artfynd/A 51189-2022 artfynd.xlsx
@@ -1877,7 +1877,7 @@
         <v>135864904</v>
       </c>
       <c r="B12" t="n">
-        <v>58869</v>
+        <v>58882</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3181,7 +3181,7 @@
         <v>135864905</v>
       </c>
       <c r="B22" t="n">
-        <v>58866</v>
+        <v>58879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135864906</v>
       </c>
       <c r="B41" t="n">
-        <v>58855</v>
+        <v>58868</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>135864917</v>
       </c>
       <c r="B42" t="n">
-        <v>58855</v>
+        <v>58868</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
